--- a/data/trans_camb/IP04D$individual-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Estudios-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 2,85</t>
+          <t>-15,65; 2,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,15; -0,62</t>
+          <t>-18,67; -1,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 2,4</t>
+          <t>-15,26; 3,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 15,98</t>
+          <t>-7,92; 16,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 0,66</t>
+          <t>-12,68; 0,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 5,93</t>
+          <t>-10,75; 5,39</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-69,23; 22,42</t>
+          <t>-70,65; 21,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,28; 2,1</t>
+          <t>-84,24; -4,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,04; 26,21</t>
+          <t>-69,49; 31,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,74; 126,72</t>
+          <t>-40,08; 141,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,75; 5,22</t>
+          <t>-61,56; 8,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,15; 44,66</t>
+          <t>-53,33; 37,24</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 8,93</t>
+          <t>-0,19; 9,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,32; -8,26</t>
+          <t>-16,87; -7,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 3,34</t>
+          <t>-6,09; 3,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,37; -5,88</t>
+          <t>-17,78; -5,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 4,97</t>
+          <t>-2,03; 4,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,15; -8,69</t>
+          <t>-16,51; -9,08</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 38,34</t>
+          <t>-0,72; 39,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,8; -35,15</t>
+          <t>-60,96; -33,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 12,2</t>
+          <t>-18,91; 11,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,01; -19,0</t>
+          <t>-55,88; -18,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 19,52</t>
+          <t>-6,71; 17,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,06; -31,75</t>
+          <t>-55,5; -32,88</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 12,83</t>
+          <t>-5,16; 12,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,08; -3,82</t>
+          <t>-20,96; -3,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,33; -0,84</t>
+          <t>-17,36; -0,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,44; -6,46</t>
+          <t>-22,65; -5,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 2,72</t>
+          <t>-9,73; 2,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,09; -6,87</t>
+          <t>-19,6; -7,38</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 35,16</t>
+          <t>-11,79; 35,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,49; -10,19</t>
+          <t>-47,23; -8,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,69; -2,09</t>
+          <t>-35,39; -1,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,74; -14,8</t>
+          <t>-46,48; -12,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,53; 6,79</t>
+          <t>-21,53; 6,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,98; -17,12</t>
+          <t>-42,54; -17,86</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,48</t>
+          <t>-0,24; 7,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,31; -8,49</t>
+          <t>-16,25; -8,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 0,74</t>
+          <t>-6,93; 0,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,26; -5,58</t>
+          <t>-15,21; -6,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 3,11</t>
+          <t>-2,86; 3,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,74; -8,44</t>
+          <t>-14,38; -8,36</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 28,47</t>
+          <t>-0,83; 28,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,39; -32,26</t>
+          <t>-54,88; -32,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 2,67</t>
+          <t>-20,89; 2,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,79; -18,31</t>
+          <t>-45,63; -20,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 10,86</t>
+          <t>-8,95; 10,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,78; -29,11</t>
+          <t>-46,39; -28,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$individual-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Estudios-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 2,3</t>
+          <t>-15,58; 3,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,67; -1,04</t>
+          <t>-19,01; -1,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 3,17</t>
+          <t>-14,88; 4,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 16,94</t>
+          <t>-8,54; 15,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 0,95</t>
+          <t>-12,57; 0,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 5,39</t>
+          <t>-10,67; 5,21</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-70,65; 21,15</t>
+          <t>-68,19; 26,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,24; -4,81</t>
+          <t>-86,68; -1,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,49; 31,52</t>
+          <t>-70,08; 46,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,08; 141,98</t>
+          <t>-40,72; 128,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 8,24</t>
+          <t>-61,11; 7,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 37,24</t>
+          <t>-53,17; 33,43</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 9,01</t>
+          <t>-0,89; 8,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,87; -7,9</t>
+          <t>-17,56; -8,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 3,05</t>
+          <t>-5,49; 3,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -5,51</t>
+          <t>-17,57; -5,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,6</t>
+          <t>-1,97; 4,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -9,08</t>
+          <t>-15,99; -8,4</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 39,85</t>
+          <t>-2,73; 38,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,96; -33,56</t>
+          <t>-62,37; -35,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 11,03</t>
+          <t>-16,99; 14,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,88; -18,87</t>
+          <t>-55,32; -17,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 17,33</t>
+          <t>-6,61; 17,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,5; -32,88</t>
+          <t>-55,01; -29,91</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 12,64</t>
+          <t>-5,29; 11,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,96; -3,0</t>
+          <t>-21,54; -3,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -0,81</t>
+          <t>-18,12; -0,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,65; -5,43</t>
+          <t>-23,38; -4,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 2,64</t>
+          <t>-8,69; 3,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -7,38</t>
+          <t>-19,78; -6,48</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 35,74</t>
+          <t>-11,72; 32,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,23; -8,48</t>
+          <t>-48,43; -9,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,39; -1,95</t>
+          <t>-37,24; -2,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,48; -12,82</t>
+          <t>-47,03; -11,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 6,86</t>
+          <t>-19,45; 7,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,54; -17,86</t>
+          <t>-43,9; -16,55</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 7,45</t>
+          <t>-0,14; 7,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -8,41</t>
+          <t>-16,3; -8,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 0,7</t>
+          <t>-6,56; 1,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -6,13</t>
+          <t>-15,12; -5,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,12</t>
+          <t>-2,58; 3,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,38; -8,36</t>
+          <t>-14,67; -8,44</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 28,96</t>
+          <t>-0,58; 28,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,88; -32,37</t>
+          <t>-54,8; -30,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 2,26</t>
+          <t>-19,58; 4,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,63; -20,04</t>
+          <t>-45,85; -18,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 10,59</t>
+          <t>-8,08; 10,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,39; -28,38</t>
+          <t>-46,7; -28,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$individual-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Estudios-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción individual en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-5,65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-6,6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-10,56</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,65</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>-8,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,1</t>
+          <t>-1,81</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 3,42</t>
+          <t>-15,03; 2,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,01; -1,06</t>
+          <t>-7,96; 16,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 4,39</t>
+          <t>-14,94; 2,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 15,93</t>
+          <t>-18,77; 1,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 0,95</t>
+          <t>-12,33; 0,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 5,21</t>
+          <t>-10,08; 7,36</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-34,04%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25,09%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-35,73%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-57,16%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-34,04%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>-47,6%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-17,62%</t>
+          <t>-10,32%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,19; 26,26</t>
+          <t>-69,04; 26,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,68; -1,65</t>
+          <t>-41,3; 132,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-70,08; 46,15</t>
+          <t>-69,23; 22,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 128,63</t>
+          <t>-81,55; 25,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 7,39</t>
+          <t>-60,75; 5,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,17; 33,43</t>
+          <t>-49,6; 57,6</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-12,84</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>4,18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-12,74</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-12,67</t>
+          <t>-11,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,68</t>
+          <t>-12,33</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 8,76</t>
+          <t>-5,67; 3,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,56; -8,43</t>
+          <t>-17,53; -6,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 3,86</t>
+          <t>-1,11; 8,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,57; -5,56</t>
+          <t>-15,96; -7,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 4,72</t>
+          <t>-2,01; 4,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,99; -8,4</t>
+          <t>-15,73; -8,41</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-3,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-43,23%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>16,18%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-49,34%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,67%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-42,66%</t>
+          <t>-45,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-45,54%</t>
+          <t>-44,28%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 38,29</t>
+          <t>-17,79; 12,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,37; -35,79</t>
+          <t>-55,48; -21,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 14,41</t>
+          <t>-3,74; 38,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,32; -17,88</t>
+          <t>-57,5; -30,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 17,72</t>
+          <t>-6,7; 19,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,01; -29,91</t>
+          <t>-53,83; -31,6</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-9,53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-13,78</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>3,59</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-12,2</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-9,53</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-14,22</t>
+          <t>-12,5</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-13,11</t>
+          <t>-13,08</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 11,74</t>
+          <t>-18,33; -0,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,54; -3,62</t>
+          <t>-23,36; -6,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,12; -0,94</t>
+          <t>-5,32; 12,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,38; -4,88</t>
+          <t>-21,21; -4,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 3,06</t>
+          <t>-9,52; 2,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,78; -6,48</t>
+          <t>-18,89; -6,78</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-21,24%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-30,72%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>8,95%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-30,42%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-21,24%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-31,69%</t>
+          <t>-31,15%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-30,82%</t>
+          <t>-30,74%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 32,15</t>
+          <t>-36,69; -2,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,43; -9,96</t>
+          <t>-47,41; -14,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,24; -2,55</t>
+          <t>-11,91; 35,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,03; -11,78</t>
+          <t>-48,41; -10,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 7,72</t>
+          <t>-20,53; 6,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,9; -16,55</t>
+          <t>-42,05; -17,1</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,02</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-11,09</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>3,59</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-12,25</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,02</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-11,11</t>
+          <t>-11,29</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-11,58</t>
+          <t>-11,14</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 7,37</t>
+          <t>-6,96; 0,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,3; -8,37</t>
+          <t>-15,37; -5,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,18</t>
+          <t>-0,71; 7,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,12; -5,85</t>
+          <t>-15,05; -7,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,03</t>
+          <t>-2,72; 3,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -8,44</t>
+          <t>-14,23; -8,1</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-9,52%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-35,01%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>12,71%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-43,41%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-9,52%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-35,08%</t>
+          <t>-40,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-38,59%</t>
+          <t>-37,14%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 28,14</t>
+          <t>-20,27; 2,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,8; -30,8</t>
+          <t>-46,04; -19,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 4,22</t>
+          <t>-2,4; 28,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,85; -18,86</t>
+          <t>-50,81; -28,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 10,67</t>
+          <t>-8,54; 10,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,7; -28,58</t>
+          <t>-45,42; -28,17</t>
         </is>
       </c>
     </row>
